--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484570_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484570_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5501</v>
+        <v>1.962</v>
       </c>
       <c r="E2" t="n">
-        <v>0.203</v>
+        <v>0.7388</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3471</v>
+        <v>1.2232</v>
       </c>
       <c r="G2" t="n">
         <v>1.192</v>
@@ -610,13 +610,13 @@
         <v>0.733</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3933</v>
+        <v>0.0187</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4223</v>
+        <v>0.1135</v>
       </c>
       <c r="U2" t="n">
-        <v>0.029</v>
+        <v>-0.0948</v>
       </c>
       <c r="V2" t="n">
         <v>0.9346</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. VANOUKIA</t>
+          <t>A. ALVAREZ LENCINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.0263</v>
+        <v>-0.8613</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5757</v>
+        <v>0.6978</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.602</v>
+        <v>-1.5591</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0042</v>
+        <v>-4.4138</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2608</v>
+        <v>-2.019</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2566</v>
+        <v>-2.3948</v>
       </c>
       <c r="J4" t="n">
-        <v>2.189</v>
+        <v>-0.866</v>
       </c>
       <c r="K4" t="n">
-        <v>2.195</v>
+        <v>-0.2666</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0061</v>
+        <v>-0.5994</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1848</v>
+        <v>-3.5478</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9342</v>
+        <v>-1.7523</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2505</v>
+        <v>-1.7955</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.2828</v>
+        <v>2.0158</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8754</v>
+        <v>-0.0418</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8583</v>
+        <v>-0.3367</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0172</v>
+        <v>0.2949</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6231</v>
+        <v>1.5785</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2774</v>
+        <v>1.9005</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.9005</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.4701</v>
+        <v>-0.9782999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9069</v>
+        <v>-1.316</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4368</v>
+        <v>0.3377</v>
       </c>
       <c r="G5" t="n">
         <v>-1.3965</v>
@@ -844,13 +844,13 @@
         <v>2.5656</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4401</v>
+        <v>-0.9483</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9374</v>
+        <v>-0.3465</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5027</v>
+        <v>-0.6018</v>
       </c>
       <c r="V5" t="n">
         <v>0.6335</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6153</v>
+        <v>-1.0577</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2517</v>
+        <v>-0.6197</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3636</v>
+        <v>-0.4379</v>
       </c>
       <c r="G6" t="n">
         <v>-1.8201</v>
@@ -922,13 +922,13 @@
         <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.0598</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4774</v>
+        <v>0.1546</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1401</v>
+        <v>-0.2144</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6439</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ALVAREZ LENCINA</t>
+          <t>M. VANOUKIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8427</v>
+        <v>-1.9797</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0854</v>
+        <v>0.8205</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7573</v>
+        <v>-2.8002</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.4138</v>
+        <v>0.0042</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.019</v>
+        <v>1.2608</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3948</v>
+        <v>-1.2566</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.866</v>
+        <v>2.189</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2666</v>
+        <v>2.195</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5994</v>
+        <v>-0.0061</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.5478</v>
+        <v>-2.1848</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7523</v>
+        <v>-0.9342</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7955</v>
+        <v>-1.2505</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0158</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0158</v>
+        <v>1.4661</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0232</v>
+        <v>-0.0781</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1199</v>
+        <v>0.103</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09669999999999999</v>
+        <v>-0.181</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5785</v>
+        <v>-0.6231</v>
       </c>
       <c r="W7" t="n">
-        <v>1.9005</v>
+        <v>1.2774</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. PAMUK</t>
+          <t>F. ROMAN MORA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4544</v>
+        <v>-2.9572</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3067</v>
+        <v>-1.8312</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7611</v>
+        <v>-1.126</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1531</v>
+        <v>-0.1915</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7743</v>
+        <v>-0.0184</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3787</v>
+        <v>-0.1731</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3278</v>
+        <v>-0.3225</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3278</v>
+        <v>0.8762</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.1987</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4808</v>
+        <v>0.1311</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1021</v>
+        <v>-0.8946</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3787</v>
+        <v>1.0256</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0158</v>
+        <v>0.9163</v>
       </c>
       <c r="S8" t="n">
-        <v>0.188</v>
+        <v>-0.2606</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8952</v>
+        <v>0.3239</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.5845</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5889</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. ROMAN MORA</t>
+          <t>H. PAMUK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6306</v>
+        <v>-3.4764</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4055</v>
+        <v>-0.6409</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2251</v>
+        <v>-2.8354</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1915</v>
+        <v>-2.1531</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0184</v>
+        <v>-0.7743</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1731</v>
+        <v>-1.3787</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3225</v>
+        <v>0.3278</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8762</v>
+        <v>0.3278</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1987</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1311</v>
+        <v>-2.4808</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8946</v>
+        <v>-1.1021</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0256</v>
+        <v>-1.3787</v>
       </c>
       <c r="P9" t="n">
+        <v>1.0995</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-0.9163</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-1.8326</v>
-      </c>
       <c r="R9" t="n">
-        <v>0.9163</v>
+        <v>2.0158</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06610000000000001</v>
+        <v>-0.8339</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7496</v>
+        <v>-0.0524</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6836</v>
+        <v>-0.7815</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5889</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. JURADO TRAVER</t>
+          <t>J. REY SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2773</v>
+        <v>-3.5575</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9608</v>
+        <v>-3.0936</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3165</v>
+        <v>-0.464</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.8346</v>
+        <v>-3.5043</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8408</v>
+        <v>-3.0109</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9938</v>
+        <v>-0.4934</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.6758</v>
+        <v>-2.3609</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3937</v>
+        <v>-1.1303</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2821</v>
+        <v>-1.2305</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1588</v>
+        <v>-1.1434</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4471</v>
+        <v>-1.8805</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2882</v>
+        <v>0.7371</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3665</v>
+        <v>-3.1154</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4661</v>
+        <v>0.5498</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0212</v>
+        <v>0.2063</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2806</v>
+        <v>0.0766</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3017</v>
+        <v>0.1297</v>
       </c>
       <c r="V10" t="n">
-        <v>0.945</v>
+        <v>2.8559</v>
       </c>
       <c r="W10" t="n">
-        <v>1.267</v>
+        <v>2.8559</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. REY SANCHEZ</t>
+          <t>L. JURADO TRAVER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1925</v>
+        <v>-3.774</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6294</v>
+        <v>-2.73</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5631</v>
+        <v>-1.044</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.5043</v>
+        <v>-3.8346</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.0109</v>
+        <v>-2.8408</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4934</v>
+        <v>-0.9938</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3609</v>
+        <v>-2.6758</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1303</v>
+        <v>-1.3937</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2305</v>
+        <v>-1.2821</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1434</v>
+        <v>-1.1588</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8805</v>
+        <v>-1.4471</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7371</v>
+        <v>0.2882</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.1154</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5498</v>
+        <v>1.4661</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4287</v>
+        <v>-0.5179</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4593</v>
+        <v>0.5113</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0306</v>
+        <v>-1.0292</v>
       </c>
       <c r="V11" t="n">
-        <v>2.8559</v>
+        <v>0.945</v>
       </c>
       <c r="W11" t="n">
-        <v>2.8559</v>
+        <v>1.267</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.7833</v>
+        <v>-7.2365</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.6105</v>
+        <v>-5.9646</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1728</v>
+        <v>-1.2719</v>
       </c>
       <c r="G12" t="n">
         <v>-5.3984</v>
@@ -1390,13 +1390,13 @@
         <v>1.4661</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7802</v>
+        <v>-0.2334</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9366</v>
+        <v>-0.2907</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1564</v>
+        <v>0.0573</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3219</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-23.4671</v>
+        <v>-22.6413</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.4895</v>
+        <v>-12.6636</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.977600000000002</v>
+        <v>-9.977600000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-20.2408</v>
@@ -1438,7 +1438,7 @@
         <v>-11.5845</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.656000000000001</v>
+        <v>-8.656000000000002</v>
       </c>
       <c r="J13" t="n">
         <v>-4.683199999999999</v>
@@ -1447,7 +1447,7 @@
         <v>1.4059</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.089200000000001</v>
+        <v>-6.0892</v>
       </c>
       <c r="M13" t="n">
         <v>-15.5572</v>
@@ -1468,13 +1468,13 @@
         <v>14.6607</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.5746</v>
+        <v>-2.7488</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5691999999999999</v>
+        <v>0.2566</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.0054</v>
+        <v>-3.0053</v>
       </c>
       <c r="V13" t="n">
         <v>2.1808</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4149</v>
+        <v>7.6961</v>
       </c>
       <c r="E14" t="n">
         <v>4.5232</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8918</v>
+        <v>3.1729</v>
       </c>
       <c r="G14" t="n">
         <v>5.8933</v>
@@ -1546,13 +1546,13 @@
         <v>2.1991</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5112</v>
+        <v>0.7924</v>
       </c>
       <c r="T14" t="n">
         <v>0.6395</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1283</v>
+        <v>0.1529</v>
       </c>
       <c r="V14" t="n">
         <v>0.6439</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>A. MONRABAL ROMEU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9844</v>
+        <v>4.7499</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6136</v>
+        <v>2.5476</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3708</v>
+        <v>2.2023</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8113</v>
+        <v>2.2258</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0162</v>
+        <v>0.0301</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8274</v>
+        <v>2.1957</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4829</v>
+        <v>2.0872</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0282</v>
+        <v>0.6286</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4546</v>
+        <v>1.4586</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2941</v>
+        <v>0.1386</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0121</v>
+        <v>-0.5985</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2821</v>
+        <v>0.7371</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0158</v>
+        <v>1.4661</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7516</v>
+        <v>1.0581</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6908</v>
+        <v>0.4604</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0608</v>
+        <v>0.5976</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1386</v>
+        <v>4.6514</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5795</v>
+        <v>3.9641</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.6872</v>
       </c>
       <c r="G16" t="n">
         <v>3.5337</v>
@@ -1702,13 +1702,13 @@
         <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6229</v>
+        <v>-0.1101</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6606</v>
+        <v>-0.276</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0377</v>
+        <v>0.1659</v>
       </c>
       <c r="V16" t="n">
         <v>0.3115</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MONRABAL ROMEU</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0914</v>
+        <v>4.0335</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0668</v>
+        <v>0.0752</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0246</v>
+        <v>3.9583</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2258</v>
+        <v>0.8113</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0301</v>
+        <v>-0.0162</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1957</v>
+        <v>0.8274</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0872</v>
+        <v>-0.4829</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6286</v>
+        <v>-0.0282</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4586</v>
+        <v>-0.4546</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1386</v>
+        <v>1.2941</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5985</v>
+        <v>0.0121</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7371</v>
+        <v>1.2821</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3995</v>
+        <v>1.8007</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0203</v>
+        <v>1.1524</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4199</v>
+        <v>0.6483</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>M. TORTAROLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7792</v>
+        <v>3.3461</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9457</v>
+        <v>3.1682</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8334</v>
+        <v>0.1778</v>
       </c>
       <c r="G18" t="n">
-        <v>3.8665</v>
+        <v>3.2546</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6964</v>
+        <v>3.2673</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1701</v>
+        <v>-0.0127</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2852</v>
+        <v>3.612</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4676</v>
+        <v>3.5605</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8176</v>
+        <v>0.0515</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5813</v>
+        <v>-0.3575</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2288</v>
+        <v>-0.2932</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3525</v>
+        <v>-0.0643</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3665</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5498</v>
+        <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5462</v>
+        <v>0.3298</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2549</v>
+        <v>0.1218</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2913</v>
+        <v>0.2079</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.267</v>
+        <v>0.3115</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5889</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. TORTAROLO</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.6739</v>
+        <v>3.1453</v>
       </c>
       <c r="E19" t="n">
-        <v>3.649</v>
+        <v>2.7534</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0249</v>
+        <v>0.3919</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2546</v>
+        <v>3.8665</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2673</v>
+        <v>2.6964</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0127</v>
+        <v>1.1701</v>
       </c>
       <c r="J19" t="n">
-        <v>3.612</v>
+        <v>3.2852</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5605</v>
+        <v>2.4676</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0515</v>
+        <v>0.8176</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3575</v>
+        <v>0.5813</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2932</v>
+        <v>0.2288</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0643</v>
+        <v>0.3525</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5498</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2828</v>
+        <v>0.5498</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6575</v>
+        <v>0.9123</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6026</v>
+        <v>0.0626</v>
       </c>
       <c r="U19" t="n">
-        <v>0.055</v>
+        <v>0.8497</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3115</v>
+        <v>-1.267</v>
       </c>
       <c r="W19" t="n">
-        <v>1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9554</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. HATHOUTI LAHRECH</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3929</v>
+        <v>1.3257</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6859</v>
+        <v>0.7716</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7069</v>
+        <v>0.5541</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1065</v>
+        <v>0.8287</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7476</v>
+        <v>-0.8093</v>
       </c>
       <c r="I20" t="n">
-        <v>0.641</v>
+        <v>1.638</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8177</v>
+        <v>1.5219</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8177</v>
+        <v>-0.4368</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.9587</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7112000000000001</v>
+        <v>-0.6932</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0701</v>
+        <v>-0.3726</v>
       </c>
       <c r="O20" t="n">
-        <v>0.641</v>
+        <v>-0.3207</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
         <v>0.9163</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1775</v>
+        <v>0.1463</v>
       </c>
       <c r="T20" t="n">
-        <v>1.776</v>
+        <v>-0.1847</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5986</v>
+        <v>0.3311</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6439</v>
+        <v>1.267</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>S. HATHOUTI LAHRECH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6147</v>
+        <v>0.9253</v>
       </c>
       <c r="E21" t="n">
-        <v>0.387</v>
+        <v>-0.0833</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2277</v>
+        <v>1.0085</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8287</v>
+        <v>-0.1065</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8093</v>
+        <v>-0.7476</v>
       </c>
       <c r="I21" t="n">
-        <v>1.638</v>
+        <v>0.641</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5219</v>
+        <v>-0.8177</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4368</v>
+        <v>-0.8177</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9587</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6932</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3726</v>
+        <v>0.0701</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3207</v>
+        <v>0.641</v>
       </c>
       <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-0.9163</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
         <v>0.9163</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5647</v>
+        <v>0.7098</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5694</v>
+        <v>1.0068</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0047</v>
+        <v>-0.297</v>
       </c>
       <c r="V21" t="n">
-        <v>1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="W21" t="n">
-        <v>1.267</v>
+        <v>0.6439</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SANCHEZ</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8154</v>
+        <v>0.3899</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.17</v>
+        <v>-0.9255</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3546</v>
+        <v>1.3154</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0205</v>
+        <v>2.1999</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2873</v>
+        <v>2.3981</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3078</v>
+        <v>-0.1982</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2208</v>
+        <v>0.57</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.446</v>
+        <v>2.3067</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6667999999999999</v>
+        <v>-1.7367</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7997</v>
+        <v>1.6299</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1587</v>
+        <v>0.0914</v>
       </c>
       <c r="O22" t="n">
-        <v>0.641</v>
+        <v>1.5385</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4661</v>
+        <v>2.3823</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5348000000000001</v>
+        <v>0.1742</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2572</v>
+        <v>0.3371</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2777</v>
+        <v>-0.1629</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9346</v>
+        <v>-2.5339</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6335</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>A. GONZALEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2244</v>
+        <v>-0.3492</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.887</v>
+        <v>-1.8816</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6626</v>
+        <v>1.5323</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1999</v>
+        <v>1.0205</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3981</v>
+        <v>-0.2873</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1982</v>
+        <v>1.3078</v>
       </c>
       <c r="J23" t="n">
-        <v>0.57</v>
+        <v>0.2208</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3067</v>
+        <v>-0.446</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.7367</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>1.6299</v>
+        <v>0.7997</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0914</v>
+        <v>0.1587</v>
       </c>
       <c r="O23" t="n">
-        <v>1.5385</v>
+        <v>0.641</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5498</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3823</v>
+        <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4401</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6244</v>
+        <v>0.0313</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8157</v>
+        <v>-0.0999</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.5339</v>
+        <v>-0.9346</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.5339</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0669</v>
+        <v>-1.7187</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7896</v>
+        <v>-0.6934</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2773</v>
+        <v>-1.0252</v>
       </c>
       <c r="G24" t="n">
         <v>-0.516</v>
@@ -2326,13 +2326,13 @@
         <v>0.3665</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6505</v>
+        <v>-0.3022</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2753</v>
+        <v>-0.1791</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3752</v>
+        <v>-0.1231</v>
       </c>
       <c r="V24" t="n">
         <v>-1.267</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.516</v>
+        <v>-2.805</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.6266</v>
+        <v>-4.242</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1105</v>
+        <v>1.4369</v>
       </c>
       <c r="G25" t="n">
         <v>-2.771</v>
@@ -2404,13 +2404,13 @@
         <v>1.0995</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.656</v>
+        <v>0.0551</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5513</v>
+        <v>-0.1666</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1047</v>
+        <v>0.2217</v>
       </c>
       <c r="V25" t="n">
         <v>0.6439</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>23.4673</v>
+        <v>25.3903</v>
       </c>
       <c r="E26" t="n">
-        <v>9.977500000000003</v>
+        <v>9.977499999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>13.4895</v>
+        <v>15.4124</v>
       </c>
       <c r="G26" t="n">
-        <v>20.2408</v>
+        <v>20.24079999999999</v>
       </c>
       <c r="H26" t="n">
         <v>11.5845</v>
@@ -2464,7 +2464,7 @@
         <v>2.5671</v>
       </c>
       <c r="M26" t="n">
-        <v>4.683300000000001</v>
+        <v>4.6833</v>
       </c>
       <c r="N26" t="n">
         <v>-1.4058</v>
@@ -2482,13 +2482,13 @@
         <v>16.4932</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5745</v>
+        <v>5.497800000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>3.0053</v>
+        <v>3.0055</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5691999999999997</v>
+        <v>2.4922</v>
       </c>
       <c r="V26" t="n">
         <v>-2.1809</v>
@@ -2497,7 +2497,7 @@
         <v>6.0754</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.256</v>
+        <v>-8.255999999999998</v>
       </c>
     </row>
   </sheetData>
